--- a/Result/profitability/2035.xlsx
+++ b/Result/profitability/2035.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.4</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.805</v>
+        <v>-0.6874999999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>-7.7</v>
+        <v>-6.27</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.64</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.635</v>
+        <v>-0.49125</v>
       </c>
       <c r="N3" t="n">
-        <v>-6.34625</v>
+        <v>-4.71375</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -795,13 +795,13 @@
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
       </c>
       <c r="T3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-1.4</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.69375</v>
+        <v>-0.5137499999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>-6.39625</v>
+        <v>-4.27</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-5.59</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.24</v>
+        <v>-1.0475</v>
       </c>
       <c r="N5" t="n">
-        <v>-15.385</v>
+        <v>-12.81</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.63</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.15375</v>
+        <v>-0.9949999999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>-14.09625</v>
+        <v>-12</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.29</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.9862499999999998</v>
+        <v>-0.8174999999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>-11.96375</v>
+        <v>-9.426250000000001</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>1.09</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.70875</v>
+        <v>-0.7224999999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>-9.15</v>
+        <v>-8.981250000000001</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1518,7 +1518,7 @@
         <v>3.92</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.26</v>
+        <v>-0.2599999999999999</v>
       </c>
       <c r="N9" t="n">
         <v>-9.036250000000001</v>
@@ -1645,10 +1645,10 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.20125</v>
+        <v>-0.2012499999999999</v>
       </c>
       <c r="N10" t="n">
-        <v>-8.712500000000002</v>
+        <v>-8.7125</v>
       </c>
       <c r="O10" t="n">
         <v>1</v>
@@ -1772,10 +1772,10 @@
         <v>0.08</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.27125</v>
+        <v>-0.2712499999999999</v>
       </c>
       <c r="N11" t="n">
-        <v>-9.285000000000002</v>
+        <v>-9.285</v>
       </c>
       <c r="O11" t="n">
         <v>1</v>
@@ -1899,10 +1899,10 @@
         <v>-0.08</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.10625</v>
+        <v>-0.1062499999999999</v>
       </c>
       <c r="N12" t="n">
-        <v>-7.982500000000003</v>
+        <v>-7.982500000000001</v>
       </c>
       <c r="O12" t="n">
         <v>1</v>
@@ -2029,7 +2029,7 @@
         <v>0.59875</v>
       </c>
       <c r="N13" t="n">
-        <v>2.698749999999998</v>
+        <v>2.69875</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2035</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>2818</v>
+      </c>
+      <c r="D75" t="n">
+        <v>2661</v>
+      </c>
+      <c r="E75" t="n">
+        <v>157</v>
+      </c>
+      <c r="F75" t="n">
+        <v>5.58</v>
+      </c>
+      <c r="G75" t="n">
+        <v>87</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>3.09%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-9</v>
+      </c>
+      <c r="J75" t="n">
+        <v>78</v>
+      </c>
+      <c r="K75" t="n">
+        <v>78</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.7275</v>
+      </c>
+      <c r="N75" t="n">
+        <v>-6.98625</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.3333333333333334</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.3191489361702127</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-1.166666666666667</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-1.37150466045273</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
